--- a/import-result.xlsx
+++ b/import-result.xlsx
@@ -7,13 +7,14 @@
     <sheet sheetId="1" name="errors" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="created" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="updated" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="skipped_existing" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
   <si>
     <t>row</t>
   </si>
@@ -24,13 +25,232 @@
     <t>error</t>
   </si>
   <si>
+    <t>6403</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "ADANI DCR TOPCON 620 WP"</t>
+  </si>
+  <si>
+    <t>6430</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR BIFACIAL 540 WP"</t>
+  </si>
+  <si>
+    <t>6433</t>
+  </si>
+  <si>
+    <t>6437</t>
+  </si>
+  <si>
+    <t>6444</t>
+  </si>
+  <si>
+    <t>7093</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR TOPCON 580 WP"</t>
+  </si>
+  <si>
+    <t>7097</t>
+  </si>
+  <si>
+    <t>7012</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "ADANI DCR BIFACIAL 550 WP"</t>
+  </si>
+  <si>
+    <t>7019</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "RAYZON DCR BIFACIAL 545 WP"</t>
+  </si>
+  <si>
+    <t>6985</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; discom_name not found: "Jharkhand Bijli Vitran Nigam Limited"; solar_panel not found: "WAAREE DCR BIFACIAL 540 WP"; inverter not found: "SOLAR YAAN 6 KW"</t>
+  </si>
+  <si>
+    <t>7062</t>
+  </si>
+  <si>
+    <t>7063</t>
+  </si>
+  <si>
+    <t>7046</t>
+  </si>
+  <si>
+    <t>7102</t>
+  </si>
+  <si>
+    <t>7103</t>
+  </si>
+  <si>
+    <t>7068</t>
+  </si>
+  <si>
+    <t>7065</t>
+  </si>
+  <si>
+    <t>7067</t>
+  </si>
+  <si>
+    <t>7073</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR BIFACIAL 540 WP"; inverter not found: "SOLAR YAAN 4 KW"</t>
+  </si>
+  <si>
+    <t>7077</t>
+  </si>
+  <si>
+    <t>7082</t>
+  </si>
+  <si>
+    <t>7085</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR TOPCON 580 WP"; inverter not found: "SOLAR YAAN 5 KW"</t>
+  </si>
+  <si>
+    <t>7091</t>
+  </si>
+  <si>
+    <t>7095</t>
+  </si>
+  <si>
+    <t>7096</t>
+  </si>
+  <si>
+    <t>7089</t>
+  </si>
+  <si>
+    <t>7092</t>
+  </si>
+  <si>
+    <t>7099</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "ADANI DCR BIFACIAL 545 WP"</t>
+  </si>
+  <si>
+    <t>7101</t>
+  </si>
+  <si>
+    <t>7214</t>
+  </si>
+  <si>
+    <t>7215</t>
+  </si>
+  <si>
+    <t>7216</t>
+  </si>
+  <si>
+    <t>7217</t>
+  </si>
+  <si>
+    <t>7218</t>
+  </si>
+  <si>
+    <t>7117</t>
+  </si>
+  <si>
+    <t>7118</t>
+  </si>
+  <si>
+    <t>7112</t>
+  </si>
+  <si>
+    <t>7119</t>
+  </si>
+  <si>
+    <t>7116</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR TOPCON 580 WP"; inverter not found: "SOLAR YAAN 4 KW"</t>
+  </si>
+  <si>
+    <t>7120</t>
+  </si>
+  <si>
+    <t>7130</t>
+  </si>
+  <si>
+    <t>7125</t>
+  </si>
+  <si>
+    <t>7131</t>
+  </si>
+  <si>
+    <t>7149</t>
+  </si>
+  <si>
+    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "RAYZON DCR BIFACIAL 545 WP"; inverter not found: "SOLAR YAAN 6 KW"</t>
+  </si>
+  <si>
+    <t>7173</t>
+  </si>
+  <si>
+    <t>7176</t>
+  </si>
+  <si>
+    <t>7178</t>
+  </si>
+  <si>
+    <t>7121</t>
+  </si>
+  <si>
+    <t>7177</t>
+  </si>
+  <si>
+    <t>7184</t>
+  </si>
+  <si>
+    <t>7190</t>
+  </si>
+  <si>
+    <t>7191</t>
+  </si>
+  <si>
+    <t>7203</t>
+  </si>
+  <si>
+    <t>7235</t>
+  </si>
+  <si>
+    <t>7236</t>
+  </si>
+  <si>
+    <t>7240</t>
+  </si>
+  <si>
+    <t>7249</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>order_number is required</t>
+  </si>
+  <si>
     <t>order_id</t>
   </si>
   <si>
-    <t>G239</t>
-  </si>
-  <si>
-    <t>G823</t>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>6031</t>
+  </si>
+  <si>
+    <t>already_in_db</t>
+  </si>
+  <si>
+    <t>6479</t>
+  </si>
+  <si>
+    <t>6976</t>
   </si>
 </sst>
 </file>
@@ -411,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -430,6 +650,644 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>42</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>43</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>50</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>51</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>52</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>53</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>54</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>55</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>56</v>
+      </c>
+      <c r="B53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>57</v>
+      </c>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>58</v>
+      </c>
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>59</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>60</v>
+      </c>
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>61</v>
+      </c>
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>62</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -438,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -454,29 +1312,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>1147</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -503,7 +1339,80 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2">
+        <v>387</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>190</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>1037</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/import-result.xlsx
+++ b/import-result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>row</t>
   </si>
@@ -28,13 +28,13 @@
     <t>6403</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "ADANI DCR TOPCON 620 WP"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Hemendrabhai ahemdabad"; handled_by_email not found: "Hemendrabhai ahemdabad"; solar_panel not found: "ADANI DCR TOPCON 620.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
   </si>
   <si>
     <t>6430</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR BIFACIAL 540 WP"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Dhaval Vihol"; handled_by_email not found: "Dhaval Vihol"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
   </si>
   <si>
     <t>6433</t>
@@ -49,39 +49,18 @@
     <t>7093</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR TOPCON 580 WP"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "WAAREE DCR TOPCON 580.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
   </si>
   <si>
     <t>7097</t>
   </si>
   <si>
-    <t>7012</t>
-  </si>
-  <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "ADANI DCR BIFACIAL 550 WP"</t>
-  </si>
-  <si>
-    <t>7019</t>
-  </si>
-  <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "RAYZON DCR BIFACIAL 545 WP"</t>
-  </si>
-  <si>
-    <t>6985</t>
-  </si>
-  <si>
-    <t>branch_name not found: "Ahmedabad"; discom_name not found: "Jharkhand Bijli Vitran Nigam Limited"; solar_panel not found: "WAAREE DCR BIFACIAL 540 WP"; inverter not found: "SOLAR YAAN 6 KW"</t>
-  </si>
-  <si>
-    <t>7062</t>
-  </si>
-  <si>
-    <t>7063</t>
-  </si>
-  <si>
     <t>7046</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Paschim Gujarat Vij Company Ltd.(PGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "ADANI DCR BIFACIAL 550.00 WP"; inverter not found: "SOLAR YAAN 4.2 KW"</t>
+  </si>
+  <si>
     <t>7102</t>
   </si>
   <si>
@@ -91,28 +70,31 @@
     <t>7068</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Torrent Power Ahmedabad"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "ADANI DCR BIFACIAL 550.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
+  </si>
+  <si>
     <t>7065</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Hemendrabhai ahemdabad"; handled_by_email not found: "Hemendrabhai ahemdabad"; solar_panel not found: "WAAREE DCR TOPCON 580.00 WP"; inverter not found: "SOLAR YAAN 4.2 KW"</t>
+  </si>
+  <si>
     <t>7067</t>
   </si>
   <si>
-    <t>7073</t>
-  </si>
-  <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR BIFACIAL 540 WP"; inverter not found: "SOLAR YAAN 4 KW"</t>
-  </si>
-  <si>
     <t>7077</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Madhya Gujarat Vij Company Ltd.(MGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Vibhav Shah"; handled_by_email not found: "Vibhav Shah"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
+  </si>
+  <si>
     <t>7082</t>
   </si>
   <si>
     <t>7085</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR TOPCON 580 WP"; inverter not found: "SOLAR YAAN 5 KW"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Torrent Power Ahmedabad"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Sachin Panchal"; handled_by_email not found: "Sachin Panchal"; solar_panel not found: "WAAREE DCR TOPCON 580.00 WP"; inverter not found: "SOLAR YAAN 5.0 KW"</t>
   </si>
   <si>
     <t>7091</t>
@@ -121,27 +103,36 @@
     <t>7095</t>
   </si>
   <si>
-    <t>7096</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "ADANI DCR BIFACIAL 550.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
   </si>
   <si>
     <t>7089</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Madhya Gujarat Vij Company Ltd.(MGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Vibhav Shah"; handled_by_email not found: "Vibhav Shah"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
+  </si>
+  <si>
     <t>7092</t>
   </si>
   <si>
     <t>7099</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "ADANI DCR BIFACIAL 545 WP"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "jigar patel"; handled_by_email not found: "jigar patel"; solar_panel not found: "ADANI DCR BIFACIAL 545.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
   </si>
   <si>
     <t>7101</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "jigar patel"; handled_by_email not found: "jigar patel"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
+  </si>
+  <si>
     <t>7214</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Hardik Patel"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "RAYZON DCR BIFACIAL 545.00 WP"; inverter not found: "SOLAR YAAN 4.2 KW"</t>
+  </si>
+  <si>
     <t>7215</t>
   </si>
   <si>
@@ -157,7 +148,7 @@
     <t>7117</t>
   </si>
   <si>
-    <t>7118</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
   </si>
   <si>
     <t>7112</t>
@@ -169,15 +160,21 @@
     <t>7116</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "WAAREE DCR TOPCON 580 WP"; inverter not found: "SOLAR YAAN 4 KW"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Madhya Gujarat Vij Company Ltd.(MGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Vibhav Shah"; handled_by_email not found: "Vibhav Shah"; solar_panel not found: "WAAREE DCR TOPCON 580.00 WP"; inverter not found: "SOLAR YAAN 4.0 KW"</t>
   </si>
   <si>
     <t>7120</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Lav Patel"; handled_by_email not found: "Lav Patel"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
+  </si>
+  <si>
     <t>7130</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Paschim Gujarat Vij Company Ltd.(PGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "ADANI DCR TOPCON 620.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
+  </si>
+  <si>
     <t>7125</t>
   </si>
   <si>
@@ -187,7 +184,7 @@
     <t>7149</t>
   </si>
   <si>
-    <t>branch_name not found: "Ahmedabad"; solar_panel not found: "RAYZON DCR BIFACIAL 545 WP"; inverter not found: "SOLAR YAAN 6 KW"</t>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Torrent Power Ahmedabad"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "RAYZON DCR BIFACIAL 545.00 WP"; inverter not found: "SOLAR YAAN 6.0 KW"</t>
   </si>
   <si>
     <t>7173</t>
@@ -202,12 +199,18 @@
     <t>7121</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Lav Patel"; handled_by_email not found: "Lav Patel"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
+  </si>
+  <si>
     <t>7177</t>
   </si>
   <si>
     <t>7184</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "National Portal"; order_type_name not found: "New"; discom_name not found: "Torrent Power Ahmedabad"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Hardik Patel"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "ADANI DCR BIFACIAL 550.00 WP"; inverter not found: "SOLAR YAAN 5.5 KW"</t>
+  </si>
+  <si>
     <t>7190</t>
   </si>
   <si>
@@ -217,40 +220,28 @@
     <t>7203</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "ADANI DCR BIFACIAL 545.00 WP"; inverter not found: "SOLAR YAAN 3.6 KW"</t>
+  </si>
+  <si>
     <t>7235</t>
   </si>
   <si>
     <t>7236</t>
   </si>
   <si>
+    <t>branch_name not found: "Gujarat"; project_scheme_name not found: "Super 60"; order_type_name not found: "New"; discom_name not found: "Uttar Gujarat Vij Company Ltd.(UGVCL)"; inquiry_source_name not found: "Individual"; inquiry_source_name not provided and default 'individual' inquiry source not found in inquiry_sources; inquiry_by_email not found: "Jayesh Prajapati"; handled_by_email not found: "Jayesh Prajapati"; solar_panel not found: "WAAREE DCR BIFACIAL 540.00 WP"; inverter not found: "SOLAR YAAN 3.3 KW"</t>
+  </si>
+  <si>
     <t>7240</t>
   </si>
   <si>
     <t>7249</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>order_number is required</t>
-  </si>
-  <si>
     <t>order_id</t>
   </si>
   <si>
     <t>reason</t>
-  </si>
-  <si>
-    <t>6031</t>
-  </si>
-  <si>
-    <t>already_in_db</t>
-  </si>
-  <si>
-    <t>6479</t>
-  </si>
-  <si>
-    <t>6976</t>
   </si>
 </sst>
 </file>
@@ -631,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -652,7 +643,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -663,7 +654,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -674,7 +665,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -685,7 +676,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -696,7 +687,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -707,7 +698,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -718,7 +709,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -729,7 +720,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -740,98 +731,98 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
         <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -839,453 +830,354 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" t="s">
         <v>61</v>
-      </c>
-      <c r="C49" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>54</v>
-      </c>
-      <c r="B51" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>55</v>
-      </c>
-      <c r="B52" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>56</v>
-      </c>
-      <c r="B53" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>57</v>
-      </c>
-      <c r="B54" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>58</v>
-      </c>
-      <c r="B55" t="s">
-        <v>67</v>
-      </c>
-      <c r="C55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>59</v>
-      </c>
-      <c r="B56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>60</v>
-      </c>
-      <c r="B57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
         <v>61</v>
-      </c>
-      <c r="B58" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>62</v>
-      </c>
-      <c r="B59" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1204,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1339,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1367,52 +1259,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
         <v>75</v>
-      </c>
-      <c r="C2">
-        <v>387</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3">
-        <v>190</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4">
-        <v>1037</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
